--- a/app/templates/report/weekly.xlsx
+++ b/app/templates/report/weekly.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\oimbra\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303487EA-0294-43C0-8CD1-6A14410D716D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067428D0-87D1-4BAC-A75D-9B46DC74AD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Weekly" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Weekly!$A$1:$AP$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Weekly!$A$1:$AQ$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="78">
   <si>
     <t>Id</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>Intermediario</t>
+  </si>
+  <si>
+    <t>Tipo</t>
   </si>
 </sst>
 </file>
@@ -763,171 +766,174 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AR4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.33203125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="34.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7" style="6" customWidth="1"/>
-    <col min="12" max="12" width="28.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="38.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="10" style="7" customWidth="1"/>
-    <col min="20" max="20" width="14.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10" style="7" customWidth="1"/>
-    <col min="23" max="24" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="48.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.5546875" style="6" customWidth="1"/>
-    <col min="28" max="28" width="8.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.88671875" style="6" customWidth="1"/>
-    <col min="30" max="30" width="9.33203125" style="6" customWidth="1"/>
-    <col min="31" max="31" width="39" style="6" bestFit="1" customWidth="1"/>
-    <col min="32" max="34" width="13.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="9.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="11" style="6" customWidth="1"/>
-    <col min="37" max="37" width="17.33203125" style="6" customWidth="1"/>
-    <col min="38" max="42" width="10" style="6" customWidth="1"/>
+    <col min="2" max="3" width="17.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.33203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="34.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="7" style="6" customWidth="1"/>
+    <col min="13" max="13" width="28.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="38.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="10" style="7" customWidth="1"/>
+    <col min="21" max="21" width="14.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="10" style="7" customWidth="1"/>
+    <col min="24" max="25" width="10" style="6" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="48.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.5546875" style="6" customWidth="1"/>
+    <col min="29" max="29" width="8.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.88671875" style="6" customWidth="1"/>
+    <col min="31" max="31" width="9.33203125" style="6" customWidth="1"/>
+    <col min="32" max="32" width="39" style="6" bestFit="1" customWidth="1"/>
+    <col min="33" max="35" width="13.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11" style="6" customWidth="1"/>
+    <col min="38" max="38" width="17.33203125" style="6" customWidth="1"/>
+    <col min="39" max="43" width="10" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="10" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" s="10" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="K1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="M1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="N1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="O1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="P1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="Q1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="R1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="S1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="T1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="U1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="V1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="11" t="s">
+      <c r="W1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="X1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="Y1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="11" t="s">
+      <c r="Z1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="12" t="s">
+      <c r="AA1" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="12" t="s">
+      <c r="AB1" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="11" t="s">
+      <c r="AC1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="11" t="s">
+      <c r="AD1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="AE1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="11" t="s">
+      <c r="AF1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="11" t="s">
+      <c r="AG1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="11" t="s">
+      <c r="AH1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="11" t="s">
+      <c r="AI1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="11" t="s">
+      <c r="AJ1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="12" t="s">
+      <c r="AK1" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="13" t="s">
+      <c r="AL1" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="13" t="s">
+      <c r="AM1" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="13" t="s">
+      <c r="AN1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="13" t="s">
+      <c r="AO1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="13" t="s">
+      <c r="AP1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="13" t="s">
+      <c r="AQ1" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:43" ht="50.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" ht="50.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
@@ -946,31 +952,31 @@
       <c r="F2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="G2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="L2" s="1" t="s">
         <v>41</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="P2" s="1" t="s">
         <v>41</v>
       </c>
@@ -983,8 +989,8 @@
       <c r="S2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>42</v>
+      <c r="T2" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>42</v>
@@ -998,8 +1004,8 @@
       <c r="X2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Y2" s="1" t="s">
-        <v>41</v>
+      <c r="Y2" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>41</v>
@@ -1007,14 +1013,14 @@
       <c r="AA2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AB2" s="2" t="s">
-        <v>42</v>
+      <c r="AB2" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="AC2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AD2" s="1" t="s">
-        <v>41</v>
+      <c r="AD2" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>41</v>
@@ -1052,8 +1058,11 @@
       <c r="AP2" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="AQ2" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="3" spans="1:43" ht="50.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:44" ht="50.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>43</v>
       </c>
@@ -1061,107 +1070,110 @@
         <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="3"/>
+      <c r="L3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="3"/>
+      <c r="P3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="S3" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="T3" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="T3" s="3"/>
-      <c r="U3" s="4"/>
+      <c r="U3" s="3"/>
       <c r="V3" s="4"/>
-      <c r="W3" s="3"/>
+      <c r="W3" s="4"/>
       <c r="X3" s="3"/>
-      <c r="Y3" s="3" t="s">
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="AA3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AA3" s="3" t="s">
+      <c r="AB3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AB3" s="3"/>
       <c r="AC3" s="3"/>
-      <c r="AD3" s="3" t="s">
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AF3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="AF3" s="3" t="s">
+      <c r="AG3" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AG3" s="3" t="s">
+      <c r="AH3" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AH3" s="3" t="s">
+      <c r="AI3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="AI3" s="3" t="s">
+      <c r="AJ3" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AJ3" s="3" t="s">
+      <c r="AK3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="AK3" s="3" t="s">
+      <c r="AL3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="AL3" s="3" t="s">
+      <c r="AM3" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="AM3" s="3" t="s">
+      <c r="AN3" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AN3" s="3" t="s">
+      <c r="AO3" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="AO3" s="3" t="s">
+      <c r="AP3" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="AP3" s="3" t="s">
+      <c r="AQ3" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -1171,70 +1183,68 @@
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="15" t="e">
-        <f ca="1">IF(AL4&lt;&gt;"",ROUNDDOWN((NOW()-AL4)/365,0),"")</f>
+      <c r="J4" s="5"/>
+      <c r="K4" s="15" t="e">
+        <f ca="1">IF(AM4&lt;&gt;"",ROUNDDOWN((NOW()-AM4)/365,0),"")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K4" s="5"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="5" t="str">
-        <f t="shared" ref="N4" si="0">IF(L4="España","NATIONAL","INTERNATIONAL")</f>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5" t="str">
+        <f t="shared" ref="O4" si="0">IF(M4="España","NATIONAL","INTERNATIONAL")</f>
         <v>INTERNATIONAL</v>
       </c>
-      <c r="O4" s="5"/>
       <c r="P4" s="5"/>
-      <c r="Q4" s="14" t="s">
-        <v>75</v>
-      </c>
+      <c r="Q4" s="5"/>
       <c r="R4" s="14" t="s">
         <v>75</v>
       </c>
       <c r="S4" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="T4" s="15" t="e">
-        <f>U4-R4</f>
+      <c r="T4" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="U4" s="15" t="e">
+        <f>V4-S4</f>
         <v>#VALUE!</v>
       </c>
-      <c r="U4" s="14" t="str">
-        <f t="shared" ref="U4" si="1">IF(AO4&lt;&gt;"",AO4,AM4)</f>
+      <c r="V4" s="14" t="str">
+        <f t="shared" ref="V4" si="1">IF(AP4&lt;&gt;"",AP4,AN4)</f>
         <v>date</v>
       </c>
-      <c r="V4" s="14" t="str">
-        <f t="shared" ref="V4" si="2">IF(AP4&lt;&gt;"",AP4,AN4)</f>
+      <c r="W4" s="14" t="str">
+        <f t="shared" ref="W4" si="2">IF(AQ4&lt;&gt;"",AQ4,AO4)</f>
         <v>date</v>
       </c>
-      <c r="W4" s="15" t="e">
-        <f t="shared" ref="W4" si="3">V4-U4</f>
+      <c r="X4" s="15" t="e">
+        <f t="shared" ref="X4" si="3">W4-V4</f>
         <v>#VALUE!</v>
       </c>
-      <c r="X4" s="15" t="e">
-        <f t="shared" ref="X4" si="4">MROUND(W4/30,0.5)</f>
+      <c r="Y4" s="15" t="e">
+        <f t="shared" ref="Y4" si="4">MROUND(X4/30,0.5)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Y4" s="5"/>
       <c r="Z4" s="5"/>
       <c r="AA4" s="5"/>
-      <c r="AB4" s="5" t="str">
-        <f t="shared" ref="AB4" si="5">MID(AK4,8,5)</f>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5" t="str">
+        <f t="shared" ref="AC4" si="5">MID(AL4,8,5)</f>
         <v/>
       </c>
-      <c r="AC4" s="5" t="str">
-        <f t="shared" ref="AC4" si="6">MID(AK4,14,9)</f>
+      <c r="AD4" s="5" t="str">
+        <f t="shared" ref="AD4" si="6">MID(AL4,14,9)</f>
         <v/>
       </c>
-      <c r="AD4" s="5"/>
       <c r="AE4" s="5"/>
-      <c r="AF4" s="9"/>
+      <c r="AF4" s="5"/>
       <c r="AG4" s="9"/>
       <c r="AH4" s="9"/>
-      <c r="AI4" s="5"/>
-      <c r="AJ4" s="9"/>
-      <c r="AK4" s="5"/>
-      <c r="AL4" s="14" t="s">
-        <v>75</v>
-      </c>
+      <c r="AI4" s="9"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="9"/>
+      <c r="AL4" s="5"/>
       <c r="AM4" s="14" t="s">
         <v>75</v>
       </c>
@@ -1247,13 +1257,16 @@
       <c r="AP4" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AQ4" s="16"/>
+      <c r="AQ4" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR4" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AQ1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="T4" evalError="1"/>
+    <ignoredError sqref="U4" evalError="1"/>
   </ignoredErrors>
 </worksheet>
 </file>